--- a/NEW BOT 02/Inter_Sales_Requisition_Report.xlsx
+++ b/NEW BOT 02/Inter_Sales_Requisition_Report.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -47,15 +47,21 @@
     <font>
       <name val="Segoe UI"/>
       <b val="1"/>
-      <color rgb="00B45309"/>
+      <color rgb="00137333"/>
       <sz val="9.5"/>
     </font>
     <font>
       <name val="Segoe UI"/>
       <sz val="9.5"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00B45309"/>
+      <sz val="9.5"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -82,8 +88,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FEF3C7"/>
-        <bgColor rgb="00FEF3C7"/>
+        <fgColor rgb="00E6F4EA"/>
+        <bgColor rgb="00E6F4EA"/>
       </patternFill>
     </fill>
     <fill>
@@ -96,6 +102,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00EAF5EA"/>
         <bgColor rgb="00EAF5EA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF3C7"/>
+        <bgColor rgb="00FEF3C7"/>
       </patternFill>
     </fill>
   </fills>
@@ -139,7 +151,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -175,6 +187,9 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="3" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -554,7 +569,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -580,7 +595,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Destination: FAN  |  Date Range: 2026-08-15 to 2026-08-30  |  Total Requisitions: 9  |  Generated: 2026-09-19 17:11:12</t>
+          <t>Destination: FAN  |  Date Range: 2026-09-01 to 2026-09-21  |  Total Requisitions: 8  |  Generated: 2026-09-21 09:41:37</t>
         </is>
       </c>
     </row>
@@ -644,12 +659,12 @@
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2291</t>
+          <t>2339</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -659,46 +674,46 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>MEP</t>
+          <t>Printing and Packaging</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>Md. Rabbi Howladar</t>
+          <t>Md. Saiful Islam</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>UNCHECKED</t>
         </is>
       </c>
       <c r="H5" s="7" t="n">
-        <v>166200</v>
+        <v>42825</v>
       </c>
       <c r="I5" s="7" t="n">
-        <v>94259</v>
+        <v>0</v>
       </c>
       <c r="J5" s="7" t="n">
-        <v>71941</v>
+        <v>42825</v>
       </c>
       <c r="K5" s="8" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>2290</t>
+          <t>2338</t>
         </is>
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="C6" s="10" t="inlineStr">
@@ -713,41 +728,41 @@
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="F6" s="10" t="inlineStr">
         <is>
-          <t>Md. Rabbi Howladar</t>
+          <t>Md. Saiful Islam</t>
         </is>
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>UNCHECKED</t>
         </is>
       </c>
       <c r="H6" s="11" t="n">
-        <v>7800</v>
+        <v>453400</v>
       </c>
       <c r="I6" s="11" t="n">
-        <v>7513</v>
+        <v>0</v>
       </c>
       <c r="J6" s="11" t="n">
-        <v>287</v>
+        <v>453400</v>
       </c>
       <c r="K6" s="12" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2289</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -762,27 +777,27 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>Md. Rabbi Howladar</t>
+          <t>Md. Saiful Islam</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>UNCHECKED</t>
         </is>
       </c>
       <c r="H7" s="7" t="n">
-        <v>115</v>
+        <v>30000</v>
       </c>
       <c r="I7" s="7" t="n">
-        <v>115</v>
+        <v>0</v>
       </c>
       <c r="J7" s="7" t="n">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="K7" s="8" t="n">
         <v>1</v>
@@ -791,12 +806,12 @@
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>2288</t>
+          <t>2336</t>
         </is>
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="C8" s="10" t="inlineStr">
@@ -806,46 +821,46 @@
       </c>
       <c r="D8" s="10" t="inlineStr">
         <is>
-          <t>MEP</t>
+          <t>Printing and Packaging</t>
         </is>
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="F8" s="10" t="inlineStr">
         <is>
-          <t>Md. Rabbi Howladar</t>
+          <t>Md. Saiful Islam</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>UNCHECKED</t>
         </is>
       </c>
       <c r="H8" s="11" t="n">
-        <v>103700</v>
+        <v>307850</v>
       </c>
       <c r="I8" s="11" t="n">
-        <v>39530</v>
+        <v>0</v>
       </c>
       <c r="J8" s="11" t="n">
-        <v>64170</v>
+        <v>307850</v>
       </c>
       <c r="K8" s="12" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2287</t>
+          <t>2335</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -860,7 +875,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
@@ -870,31 +885,31 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>CHECKED</t>
         </is>
       </c>
       <c r="H9" s="7" t="n">
-        <v>176709</v>
+        <v>102700</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>116051.1</v>
+        <v>0</v>
       </c>
       <c r="J9" s="7" t="n">
-        <v>60657.9</v>
+        <v>102700</v>
       </c>
       <c r="K9" s="8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>2286</t>
+          <t>2334</t>
         </is>
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="C10" s="10" t="inlineStr">
@@ -909,7 +924,7 @@
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="F10" s="10" t="inlineStr">
@@ -919,31 +934,31 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>CHECKED</t>
         </is>
       </c>
       <c r="H10" s="11" t="n">
-        <v>40000</v>
+        <v>141530</v>
       </c>
       <c r="I10" s="11" t="n">
-        <v>20596</v>
+        <v>0</v>
       </c>
       <c r="J10" s="11" t="n">
-        <v>19404</v>
+        <v>141530</v>
       </c>
       <c r="K10" s="12" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2285</t>
+          <t>2333</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -958,7 +973,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
@@ -968,31 +983,31 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>CHECKED</t>
         </is>
       </c>
       <c r="H11" s="7" t="n">
-        <v>420000</v>
+        <v>322375</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>274853</v>
+        <v>0</v>
       </c>
       <c r="J11" s="7" t="n">
-        <v>145147</v>
+        <v>322375</v>
       </c>
       <c r="K11" s="8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>2283</t>
+          <t>2326</t>
         </is>
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="C12" s="10" t="inlineStr">
@@ -1007,7 +1022,7 @@
       </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="F12" s="10" t="inlineStr">
@@ -1015,96 +1030,47 @@
           <t>Md. Rabbi Howladar</t>
         </is>
       </c>
-      <c r="G12" s="6" t="inlineStr">
+      <c r="G12" s="13" t="inlineStr">
         <is>
           <t>PENDING</t>
         </is>
       </c>
       <c r="H12" s="11" t="n">
-        <v>466260</v>
+        <v>392500</v>
       </c>
       <c r="I12" s="11" t="n">
-        <v>336696</v>
+        <v>359012</v>
       </c>
       <c r="J12" s="11" t="n">
-        <v>129564</v>
+        <v>33488</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>2282</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>FAN</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>Printing and Packaging</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>Md. Rabbi Howladar</t>
-        </is>
-      </c>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H13" s="7" t="n">
-        <v>279840</v>
-      </c>
-      <c r="I13" s="7" t="n">
-        <v>267209.3</v>
-      </c>
-      <c r="J13" s="7" t="n">
-        <v>12630.7</v>
-      </c>
-      <c r="K13" s="8" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="13" t="inlineStr">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" ht="24" customHeight="1">
+      <c r="A13" s="14" t="inlineStr">
         <is>
           <t>TOTAL SUMMARY</t>
         </is>
       </c>
-      <c r="H14" s="14" t="n">
-        <v>1660624</v>
-      </c>
-      <c r="I14" s="14" t="n">
-        <v>1156822.4</v>
-      </c>
-      <c r="J14" s="14" t="n">
-        <v>503801.6</v>
-      </c>
-      <c r="K14" s="15" t="n">
-        <v>90</v>
+      <c r="H13" s="15" t="n">
+        <v>1793180</v>
+      </c>
+      <c r="I13" s="15" t="n">
+        <v>359012</v>
+      </c>
+      <c r="J13" s="15" t="n">
+        <v>1434168</v>
+      </c>
+      <c r="K13" s="16" t="n">
+        <v>84</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A14:G14"/>
+    <mergeCell ref="A13:G13"/>
     <mergeCell ref="A1:K1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1117,7 +1083,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I91"/>
+  <dimension ref="A1:I85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1132,47 +1098,47 @@
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="16" t="inlineStr">
+      <c r="A1" s="17" t="inlineStr">
         <is>
           <t>Req No</t>
         </is>
       </c>
-      <c r="B1" s="16" t="inlineStr">
+      <c r="B1" s="17" t="inlineStr">
         <is>
           <t>Req Date</t>
         </is>
       </c>
-      <c r="C1" s="16" t="inlineStr">
+      <c r="C1" s="17" t="inlineStr">
         <is>
           <t>SL</t>
         </is>
       </c>
-      <c r="D1" s="16" t="inlineStr">
+      <c r="D1" s="17" t="inlineStr">
         <is>
           <t>Item Code</t>
         </is>
       </c>
-      <c r="E1" s="16" t="inlineStr">
+      <c r="E1" s="17" t="inlineStr">
         <is>
           <t>Item Description</t>
         </is>
       </c>
-      <c r="F1" s="16" t="inlineStr">
+      <c r="F1" s="17" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="G1" s="16" t="inlineStr">
+      <c r="G1" s="17" t="inlineStr">
         <is>
           <t>Req Qty</t>
         </is>
       </c>
-      <c r="H1" s="16" t="inlineStr">
+      <c r="H1" s="17" t="inlineStr">
         <is>
           <t>Issue Qty</t>
         </is>
       </c>
-      <c r="I1" s="16" t="inlineStr">
+      <c r="I1" s="17" t="inlineStr">
         <is>
           <t>Pending Qty</t>
         </is>
@@ -1181,12 +1147,12 @@
     <row r="2" ht="19" customHeight="1">
       <c r="A2" s="9" t="inlineStr">
         <is>
-          <t>2291</t>
+          <t>2339</t>
         </is>
       </c>
       <c r="B2" s="9" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="C2" s="9" t="inlineStr">
@@ -1196,38 +1162,38 @@
       </c>
       <c r="D2" s="9" t="inlineStr">
         <is>
-          <t>3102010001</t>
+          <t>3202010001</t>
         </is>
       </c>
       <c r="E2" s="10" t="inlineStr">
         <is>
-          <t>Exhaust Fan Base (8``)</t>
+          <t>HDPE Poly (L=22``, W=18``, T=0.025mm)</t>
         </is>
       </c>
       <c r="F2" s="9" t="inlineStr">
         <is>
-          <t>Pcs</t>
+          <t>KG</t>
         </is>
       </c>
       <c r="G2" s="11" t="n">
-        <v>5775</v>
+        <v>100</v>
       </c>
       <c r="H2" s="11" t="n">
-        <v>5175</v>
+        <v>0</v>
       </c>
       <c r="I2" s="11" t="n">
-        <v>600</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>2291</t>
+          <t>2339</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -1237,38 +1203,38 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>3102010002</t>
+          <t>3202010008</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>Exhaust Fan Cover (8``)</t>
+          <t>HDPE Poly (L=24``, W=20``, T=0.025mm)</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>Pcs</t>
+          <t>KG</t>
         </is>
       </c>
       <c r="G3" s="7" t="n">
-        <v>5775</v>
+        <v>125</v>
       </c>
       <c r="H3" s="7" t="n">
-        <v>5775</v>
+        <v>0</v>
       </c>
       <c r="I3" s="7" t="n">
-        <v>0</v>
+        <v>125</v>
       </c>
     </row>
     <row r="4" ht="19" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
         <is>
-          <t>2291</t>
+          <t>2339</t>
         </is>
       </c>
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="C4" s="9" t="inlineStr">
@@ -1278,12 +1244,12 @@
       </c>
       <c r="D4" s="9" t="inlineStr">
         <is>
-          <t>3102010003</t>
+          <t>3201010079</t>
         </is>
       </c>
       <c r="E4" s="10" t="inlineStr">
         <is>
-          <t>Exhaust Fan Shutter (8``)</t>
+          <t>8 Inch Exhaust Fan Body Carton (Alu)</t>
         </is>
       </c>
       <c r="F4" s="9" t="inlineStr">
@@ -1292,24 +1258,24 @@
         </is>
       </c>
       <c r="G4" s="11" t="n">
-        <v>17325</v>
+        <v>5775</v>
       </c>
       <c r="H4" s="11" t="n">
-        <v>12940</v>
+        <v>0</v>
       </c>
       <c r="I4" s="11" t="n">
-        <v>4385</v>
+        <v>5775</v>
       </c>
     </row>
     <row r="5" ht="19" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2291</t>
+          <t>2339</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -1319,12 +1285,12 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>3102010004</t>
+          <t>3201010080</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>Exhaust Fan Blade (8``)</t>
+          <t>10 Inch Exhaust Fan Body Carton (Alu)</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -1333,24 +1299,24 @@
         </is>
       </c>
       <c r="G5" s="7" t="n">
-        <v>5775</v>
+        <v>6825</v>
       </c>
       <c r="H5" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I5" s="7" t="n">
-        <v>5775</v>
+        <v>6825</v>
       </c>
     </row>
     <row r="6" ht="19" customHeight="1">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>2291</t>
+          <t>2339</t>
         </is>
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="C6" s="9" t="inlineStr">
@@ -1360,12 +1326,12 @@
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>3102010005</t>
+          <t>3201010081</t>
         </is>
       </c>
       <c r="E6" s="10" t="inlineStr">
         <is>
-          <t>Exhaust Fan Side Stand (8``)</t>
+          <t>Aero Flow Sticker</t>
         </is>
       </c>
       <c r="F6" s="9" t="inlineStr">
@@ -1374,24 +1340,24 @@
         </is>
       </c>
       <c r="G6" s="11" t="n">
-        <v>5775</v>
+        <v>15000</v>
       </c>
       <c r="H6" s="11" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="I6" s="11" t="n">
-        <v>5690</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="7" ht="19" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2291</t>
+          <t>2339</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -1401,12 +1367,12 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>3102010006</t>
+          <t>3201010083</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>Exhaust Fan Show Cap With Pitol Bush</t>
+          <t>Warranty Card (Aero Flow)</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -1415,39 +1381,39 @@
         </is>
       </c>
       <c r="G7" s="7" t="n">
-        <v>12600</v>
+        <v>15000</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>9638</v>
+        <v>0</v>
       </c>
       <c r="I7" s="7" t="n">
-        <v>2962</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="8" ht="19" customHeight="1">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>2291</t>
+          <t>2338</t>
         </is>
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>3102010007</t>
+          <t>3102010001</t>
         </is>
       </c>
       <c r="E8" s="10" t="inlineStr">
         <is>
-          <t>Exhaust Fan Capacitor Box</t>
+          <t>Exhaust Fan Base (8``)</t>
         </is>
       </c>
       <c r="F8" s="9" t="inlineStr">
@@ -1456,39 +1422,39 @@
         </is>
       </c>
       <c r="G8" s="11" t="n">
-        <v>12600</v>
+        <v>5775</v>
       </c>
       <c r="H8" s="11" t="n">
-        <v>5521</v>
+        <v>0</v>
       </c>
       <c r="I8" s="11" t="n">
-        <v>7079</v>
+        <v>5775</v>
       </c>
     </row>
     <row r="9" ht="19" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2291</t>
+          <t>2338</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>3102010008</t>
+          <t>3102010002</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>Exhaust Fan Stick (8``)</t>
+          <t>Exhaust Fan Cover (8``)</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -1500,36 +1466,36 @@
         <v>5775</v>
       </c>
       <c r="H9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="7" t="n">
         <v>5775</v>
-      </c>
-      <c r="I9" s="7" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="10" ht="19" customHeight="1">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>2291</t>
+          <t>2338</t>
         </is>
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>3102010009</t>
+          <t>3102010003</t>
         </is>
       </c>
       <c r="E10" s="10" t="inlineStr">
         <is>
-          <t>Exhaust Fan Clam</t>
+          <t>Exhaust Fan Shutter (8``)</t>
         </is>
       </c>
       <c r="F10" s="9" t="inlineStr">
@@ -1538,39 +1504,39 @@
         </is>
       </c>
       <c r="G10" s="11" t="n">
-        <v>12600</v>
+        <v>17325</v>
       </c>
       <c r="H10" s="11" t="n">
         <v>0</v>
       </c>
       <c r="I10" s="11" t="n">
-        <v>12600</v>
+        <v>17325</v>
       </c>
     </row>
     <row r="11" ht="19" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2291</t>
+          <t>2338</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>3102010011</t>
+          <t>3102010004</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>Exhaust Fan Spring Lock</t>
+          <t>Exhaust Fan Blade (8``)</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -1579,39 +1545,39 @@
         </is>
       </c>
       <c r="G11" s="7" t="n">
-        <v>12600</v>
+        <v>5775</v>
       </c>
       <c r="H11" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>12600</v>
+        <v>5775</v>
       </c>
     </row>
     <row r="12" ht="19" customHeight="1">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>2291</t>
+          <t>2338</t>
         </is>
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>3202010010</t>
+          <t>3102010005</t>
         </is>
       </c>
       <c r="E12" s="10" t="inlineStr">
         <is>
-          <t>Exhaust Fan Base (10``)</t>
+          <t>Exhaust Fan Side Stand (8``)</t>
         </is>
       </c>
       <c r="F12" s="9" t="inlineStr">
@@ -1620,39 +1586,39 @@
         </is>
       </c>
       <c r="G12" s="11" t="n">
-        <v>6825</v>
+        <v>5775</v>
       </c>
       <c r="H12" s="11" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I12" s="11" t="n">
-        <v>6725</v>
+        <v>5775</v>
       </c>
     </row>
     <row r="13" ht="19" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2291</t>
+          <t>2338</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>3202010011</t>
+          <t>3102010006</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>Exhaust Fan Cover (10``)</t>
+          <t>Exhaust Fan Show Cap With Pitol Bush</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
@@ -1661,39 +1627,39 @@
         </is>
       </c>
       <c r="G13" s="7" t="n">
-        <v>6825</v>
+        <v>12600</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>2143</v>
+        <v>0</v>
       </c>
       <c r="I13" s="7" t="n">
-        <v>4682</v>
+        <v>12600</v>
       </c>
     </row>
     <row r="14" ht="19" customHeight="1">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>2291</t>
+          <t>2338</t>
         </is>
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>3202010012</t>
+          <t>3102010007</t>
         </is>
       </c>
       <c r="E14" s="10" t="inlineStr">
         <is>
-          <t>Exhaust Fan Side Stand (10``)</t>
+          <t>Exhaust Fan Capacitor Box</t>
         </is>
       </c>
       <c r="F14" s="9" t="inlineStr">
@@ -1702,39 +1668,39 @@
         </is>
       </c>
       <c r="G14" s="11" t="n">
-        <v>6825</v>
+        <v>12600</v>
       </c>
       <c r="H14" s="11" t="n">
-        <v>4807</v>
+        <v>0</v>
       </c>
       <c r="I14" s="11" t="n">
-        <v>2018</v>
+        <v>12600</v>
       </c>
     </row>
     <row r="15" ht="19" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2291</t>
+          <t>2338</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>3202010013</t>
+          <t>3102010008</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>Exhaust Fan Shutter (10``)</t>
+          <t>Exhaust Fan Stick (8``)</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
@@ -1743,39 +1709,39 @@
         </is>
       </c>
       <c r="G15" s="7" t="n">
-        <v>20475</v>
+        <v>20000</v>
       </c>
       <c r="H15" s="7" t="n">
-        <v>20475</v>
+        <v>0</v>
       </c>
       <c r="I15" s="7" t="n">
-        <v>0</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="16" ht="19" customHeight="1">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>2291</t>
+          <t>2338</t>
         </is>
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>3202010014</t>
+          <t>3102010009</t>
         </is>
       </c>
       <c r="E16" s="10" t="inlineStr">
         <is>
-          <t>Exhaust Fan Stick (10``)</t>
+          <t>Exhaust Fan Clam</t>
         </is>
       </c>
       <c r="F16" s="9" t="inlineStr">
@@ -1784,39 +1750,39 @@
         </is>
       </c>
       <c r="G16" s="11" t="n">
-        <v>6825</v>
+        <v>100000</v>
       </c>
       <c r="H16" s="11" t="n">
-        <v>6825</v>
+        <v>0</v>
       </c>
       <c r="I16" s="11" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="17" ht="19" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2291</t>
+          <t>2338</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>3202010017</t>
+          <t>3102010011</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>Exhaust Fan Blade (10``)</t>
+          <t>Exhaust Fan Spring Lock</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
@@ -1825,39 +1791,39 @@
         </is>
       </c>
       <c r="G17" s="7" t="n">
-        <v>6825</v>
+        <v>100000</v>
       </c>
       <c r="H17" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I17" s="7" t="n">
-        <v>6825</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="18" ht="19" customHeight="1">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>2291</t>
+          <t>2338</t>
         </is>
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>3102010019</t>
+          <t>3202010010</t>
         </is>
       </c>
       <c r="E18" s="10" t="inlineStr">
         <is>
-          <t>MEP Cable Tie -3.5x150mm</t>
+          <t>Exhaust Fan Base (10``)</t>
         </is>
       </c>
       <c r="F18" s="9" t="inlineStr">
@@ -1866,408 +1832,408 @@
         </is>
       </c>
       <c r="G18" s="11" t="n">
-        <v>15000</v>
+        <v>6825</v>
       </c>
       <c r="H18" s="11" t="n">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I18" s="11" t="n">
-        <v>0</v>
+        <v>6825</v>
       </c>
     </row>
     <row r="19" ht="19" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2290</t>
+          <t>2338</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>3102010012</t>
+          <t>3202010011</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>Cable 2x23/0.0076</t>
+          <t>Exhaust Fan Cover (10``)</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>Mtr</t>
+          <t>Pcs</t>
         </is>
       </c>
       <c r="G19" s="7" t="n">
-        <v>7800</v>
+        <v>6825</v>
       </c>
       <c r="H19" s="7" t="n">
-        <v>7513</v>
+        <v>0</v>
       </c>
       <c r="I19" s="7" t="n">
-        <v>287</v>
+        <v>6825</v>
       </c>
     </row>
     <row r="20" ht="19" customHeight="1">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>2289</t>
+          <t>2338</t>
         </is>
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>3102010013</t>
+          <t>3202010012</t>
         </is>
       </c>
       <c r="E20" s="10" t="inlineStr">
         <is>
-          <t>5/32 Inch, 9mm Screw</t>
+          <t>Exhaust Fan Side Stand (10``)</t>
         </is>
       </c>
       <c r="F20" s="9" t="inlineStr">
         <is>
-          <t>KG</t>
+          <t>Pcs</t>
         </is>
       </c>
       <c r="G20" s="11" t="n">
-        <v>115</v>
+        <v>6825</v>
       </c>
       <c r="H20" s="11" t="n">
-        <v>115</v>
+        <v>0</v>
       </c>
       <c r="I20" s="11" t="n">
-        <v>0</v>
+        <v>6825</v>
       </c>
     </row>
     <row r="21" ht="19" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2288</t>
+          <t>2338</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>3101010016</t>
+          <t>3202010013</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>Super Wire (SWG 33) / 0.253mm</t>
+          <t>Exhaust Fan Shutter (10``)</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>KG</t>
+          <t>Pcs</t>
         </is>
       </c>
       <c r="G21" s="7" t="n">
-        <v>8000</v>
+        <v>20475</v>
       </c>
       <c r="H21" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I21" s="7" t="n">
-        <v>8000</v>
+        <v>20475</v>
       </c>
     </row>
     <row r="22" ht="19" customHeight="1">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>2288</t>
+          <t>2338</t>
         </is>
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>3101010017</t>
+          <t>3202010014</t>
         </is>
       </c>
       <c r="E22" s="10" t="inlineStr">
         <is>
-          <t>Super Wire (SWG 34) / 0.233mm</t>
+          <t>Exhaust Fan Stick (10``)</t>
         </is>
       </c>
       <c r="F22" s="9" t="inlineStr">
         <is>
-          <t>KG</t>
+          <t>Pcs</t>
         </is>
       </c>
       <c r="G22" s="11" t="n">
-        <v>3000</v>
+        <v>20000</v>
       </c>
       <c r="H22" s="11" t="n">
         <v>0</v>
       </c>
       <c r="I22" s="11" t="n">
-        <v>3000</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="23" ht="19" customHeight="1">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>2288</t>
+          <t>2338</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>3101010018</t>
+          <t>3202010017</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>Super Wire (SWG 35) / 0.213mm</t>
+          <t>Exhaust Fan Blade (10``)</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>KG</t>
+          <t>Pcs</t>
         </is>
       </c>
       <c r="G23" s="7" t="n">
-        <v>3000</v>
+        <v>6825</v>
       </c>
       <c r="H23" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I23" s="7" t="n">
-        <v>3000</v>
+        <v>6825</v>
       </c>
     </row>
     <row r="24" ht="19" customHeight="1">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>2288</t>
+          <t>2338</t>
         </is>
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="C24" s="9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>3101010090</t>
+          <t>3102010019</t>
         </is>
       </c>
       <c r="E24" s="10" t="inlineStr">
         <is>
-          <t>Flaxible Cable 14x0.0076 - Red</t>
+          <t>MEP Cable Tie -3.5x150mm</t>
         </is>
       </c>
       <c r="F24" s="9" t="inlineStr">
         <is>
-          <t>Mtr</t>
+          <t>Pcs</t>
         </is>
       </c>
       <c r="G24" s="11" t="n">
-        <v>38400</v>
+        <v>100000</v>
       </c>
       <c r="H24" s="11" t="n">
-        <v>18230</v>
+        <v>0</v>
       </c>
       <c r="I24" s="11" t="n">
-        <v>20170</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="25" ht="19" customHeight="1">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>2288</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>3101010111</t>
+          <t>3101010107</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>Flaxible Cable 14x0.0076 - Yellow</t>
+          <t>Nice Regulator Small White(FAN)</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>Mtr</t>
+          <t>Pcs</t>
         </is>
       </c>
       <c r="G25" s="7" t="n">
-        <v>12900</v>
+        <v>30000</v>
       </c>
       <c r="H25" s="7" t="n">
-        <v>12900</v>
+        <v>0</v>
       </c>
       <c r="I25" s="7" t="n">
-        <v>0</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="26" ht="19" customHeight="1">
       <c r="A26" s="9" t="inlineStr">
         <is>
-          <t>2288</t>
+          <t>2336</t>
         </is>
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="C26" s="9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>3101010112</t>
+          <t>3201010004</t>
         </is>
       </c>
       <c r="E26" s="10" t="inlineStr">
         <is>
-          <t>Flaxible Cable 14x0.0076 - Black</t>
+          <t>Body Sticker-5601</t>
         </is>
       </c>
       <c r="F26" s="9" t="inlineStr">
         <is>
-          <t>Mtr</t>
+          <t>Pcs</t>
         </is>
       </c>
       <c r="G26" s="11" t="n">
-        <v>38400</v>
+        <v>24675</v>
       </c>
       <c r="H26" s="11" t="n">
-        <v>8400</v>
+        <v>0</v>
       </c>
       <c r="I26" s="11" t="n">
-        <v>30000</v>
+        <v>24675</v>
       </c>
     </row>
     <row r="27" ht="19" customHeight="1">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>2287</t>
+          <t>2336</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3101010070</t>
+          <t>3201010006</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>Ms Washer 3/16 (1910/kg)</t>
+          <t>Body Sticker Speed King</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>KG</t>
+          <t>Pcs</t>
         </is>
       </c>
       <c r="G27" s="7" t="n">
-        <v>15</v>
+        <v>5250</v>
       </c>
       <c r="H27" s="7" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="I27" s="7" t="n">
-        <v>7.7</v>
+        <v>5250</v>
       </c>
     </row>
     <row r="28" ht="19" customHeight="1">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>2287</t>
+          <t>2336</t>
         </is>
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="C28" s="9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t>3101010071</t>
+          <t>3201010008</t>
         </is>
       </c>
       <c r="E28" s="10" t="inlineStr">
         <is>
-          <t>Down Pipe Bolt 8mm x 1.5```` (50/kg)</t>
+          <t>Body Sticker-3601</t>
         </is>
       </c>
       <c r="F28" s="9" t="inlineStr">
@@ -2276,39 +2242,39 @@
         </is>
       </c>
       <c r="G28" s="11" t="n">
-        <v>84000</v>
+        <v>10500</v>
       </c>
       <c r="H28" s="11" t="n">
-        <v>36557</v>
+        <v>0</v>
       </c>
       <c r="I28" s="11" t="n">
-        <v>47443</v>
+        <v>10500</v>
       </c>
     </row>
     <row r="29" ht="19" customHeight="1">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>2287</t>
+          <t>2336</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3101010072</t>
+          <t>3201010010</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>Down Pipe Bolt 8mm x 2```` (45/kg)</t>
+          <t>Fan Canopy Sticker</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
@@ -2317,39 +2283,39 @@
         </is>
       </c>
       <c r="G29" s="7" t="n">
-        <v>21000</v>
+        <v>50000</v>
       </c>
       <c r="H29" s="7" t="n">
-        <v>8615</v>
+        <v>0</v>
       </c>
       <c r="I29" s="7" t="n">
-        <v>12385</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="30" ht="19" customHeight="1">
       <c r="A30" s="9" t="inlineStr">
         <is>
-          <t>2287</t>
+          <t>2336</t>
         </is>
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="C30" s="9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D30" s="9" t="inlineStr">
         <is>
-          <t>3101010073</t>
+          <t>3201010011</t>
         </is>
       </c>
       <c r="E30" s="10" t="inlineStr">
         <is>
-          <t>Down Pipe Sira Pin(Fan)</t>
+          <t>Canopy Sticker Speed King</t>
         </is>
       </c>
       <c r="F30" s="9" t="inlineStr">
@@ -2358,203 +2324,203 @@
         </is>
       </c>
       <c r="G30" s="11" t="n">
-        <v>70000</v>
+        <v>10500</v>
       </c>
       <c r="H30" s="11" t="n">
-        <v>70000</v>
+        <v>0</v>
       </c>
       <c r="I30" s="11" t="n">
-        <v>0</v>
+        <v>10500</v>
       </c>
     </row>
     <row r="31" ht="19" customHeight="1">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>2287</t>
+          <t>2336</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>3101010074</t>
+          <t>3201010013</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>Shaft/XL /Safity lock Screw 3/16x3/8```` (400/kg)</t>
+          <t>Fan Down Pipe Sticker</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>KG</t>
+          <t>Pcs</t>
         </is>
       </c>
       <c r="G31" s="7" t="n">
-        <v>126</v>
+        <v>25725</v>
       </c>
       <c r="H31" s="7" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="I31" s="7" t="n">
-        <v>34</v>
+        <v>25725</v>
       </c>
     </row>
     <row r="32" ht="19" customHeight="1">
       <c r="A32" s="9" t="inlineStr">
         <is>
-          <t>2287</t>
+          <t>2336</t>
         </is>
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="C32" s="9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D32" s="9" t="inlineStr">
         <is>
-          <t>3101010075</t>
+          <t>3201010015</t>
         </is>
       </c>
       <c r="E32" s="10" t="inlineStr">
         <is>
-          <t>Body Screw  18x6mm,H=10mm (200/kg)</t>
+          <t>Guarantee Card -5601</t>
         </is>
       </c>
       <c r="F32" s="9" t="inlineStr">
         <is>
-          <t>KG</t>
+          <t>Pcs</t>
         </is>
       </c>
       <c r="G32" s="11" t="n">
-        <v>20</v>
+        <v>25725</v>
       </c>
       <c r="H32" s="11" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I32" s="11" t="n">
-        <v>0</v>
+        <v>25725</v>
       </c>
     </row>
     <row r="33" ht="19" customHeight="1">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>2287</t>
+          <t>2336</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>3101010076</t>
+          <t>3201010017</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>Body Screw  15x6mm,H=10mm (230/kg)</t>
+          <t>Guarantee Card Speed King</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>KG</t>
+          <t>Pcs</t>
         </is>
       </c>
       <c r="G33" s="7" t="n">
-        <v>168</v>
+        <v>5250</v>
       </c>
       <c r="H33" s="7" t="n">
-        <v>105.8</v>
+        <v>0</v>
       </c>
       <c r="I33" s="7" t="n">
-        <v>62.2</v>
+        <v>5250</v>
       </c>
     </row>
     <row r="34" ht="19" customHeight="1">
       <c r="A34" s="9" t="inlineStr">
         <is>
-          <t>2287</t>
+          <t>2336</t>
         </is>
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="C34" s="9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D34" s="9" t="inlineStr">
         <is>
-          <t>3101010077</t>
+          <t>3201010019</t>
         </is>
       </c>
       <c r="E34" s="10" t="inlineStr">
         <is>
-          <t>Blade/Body Screw 12.7x6mm,H=10mm (220/kg)</t>
+          <t>Cork Sheet -5601````/4801````</t>
         </is>
       </c>
       <c r="F34" s="9" t="inlineStr">
         <is>
-          <t>KG</t>
+          <t>Pcs</t>
         </is>
       </c>
       <c r="G34" s="11" t="n">
-        <v>1380</v>
+        <v>25725</v>
       </c>
       <c r="H34" s="11" t="n">
-        <v>654</v>
+        <v>0</v>
       </c>
       <c r="I34" s="11" t="n">
-        <v>726</v>
+        <v>25725</v>
       </c>
     </row>
     <row r="35" ht="19" customHeight="1">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>2286</t>
+          <t>2336</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>3101010107</t>
+          <t>3201010020</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>Nice Regulator Small White(FAN)</t>
+          <t>Cork Sheet -5602````</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
@@ -2563,39 +2529,39 @@
         </is>
       </c>
       <c r="G35" s="7" t="n">
-        <v>40000</v>
+        <v>5250</v>
       </c>
       <c r="H35" s="7" t="n">
-        <v>20596</v>
+        <v>0</v>
       </c>
       <c r="I35" s="7" t="n">
-        <v>19404</v>
+        <v>5250</v>
       </c>
     </row>
     <row r="36" ht="19" customHeight="1">
       <c r="A36" s="9" t="inlineStr">
         <is>
-          <t>2285</t>
+          <t>2336</t>
         </is>
       </c>
       <c r="B36" s="9" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="C36" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D36" s="9" t="inlineStr">
         <is>
-          <t>3101010078</t>
+          <t>3201010021</t>
         </is>
       </c>
       <c r="E36" s="10" t="inlineStr">
         <is>
-          <t>Canopy Big</t>
+          <t>Cork Sheet -2401/3601</t>
         </is>
       </c>
       <c r="F36" s="9" t="inlineStr">
@@ -2604,39 +2570,39 @@
         </is>
       </c>
       <c r="G36" s="11" t="n">
-        <v>84000</v>
+        <v>10500</v>
       </c>
       <c r="H36" s="11" t="n">
-        <v>20115</v>
+        <v>0</v>
       </c>
       <c r="I36" s="11" t="n">
-        <v>63885</v>
+        <v>10500</v>
       </c>
     </row>
     <row r="37" ht="19" customHeight="1">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>2285</t>
+          <t>2336</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>3101010080</t>
+          <t>3201010022</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>Capacitor Cover</t>
+          <t>Body Carton -Premium (5601)-263x264x213mm</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
@@ -2645,39 +2611,39 @@
         </is>
       </c>
       <c r="G37" s="7" t="n">
-        <v>42000</v>
+        <v>24675</v>
       </c>
       <c r="H37" s="7" t="n">
-        <v>6700</v>
+        <v>0</v>
       </c>
       <c r="I37" s="7" t="n">
-        <v>35300</v>
+        <v>24675</v>
       </c>
     </row>
     <row r="38" ht="19" customHeight="1">
       <c r="A38" s="9" t="inlineStr">
         <is>
-          <t>2285</t>
+          <t>2336</t>
         </is>
       </c>
       <c r="B38" s="9" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="C38" s="9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D38" s="9" t="inlineStr">
         <is>
-          <t>3101010081</t>
+          <t>3201010023</t>
         </is>
       </c>
       <c r="E38" s="10" t="inlineStr">
         <is>
-          <t>Rubber Gasket (56`` 48``)</t>
+          <t>Body Carton Premium Gold (5603)</t>
         </is>
       </c>
       <c r="F38" s="9" t="inlineStr">
@@ -2686,39 +2652,39 @@
         </is>
       </c>
       <c r="G38" s="11" t="n">
-        <v>63000</v>
+        <v>1050</v>
       </c>
       <c r="H38" s="11" t="n">
-        <v>63000</v>
+        <v>0</v>
       </c>
       <c r="I38" s="11" t="n">
-        <v>0</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="39" ht="19" customHeight="1">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>2285</t>
+          <t>2336</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>3101010083</t>
+          <t>3201010026</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>Rubber Gasket (2401,3601)</t>
+          <t>Body Carton -Speed king (5602) -220x220x208mm</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
@@ -2727,39 +2693,39 @@
         </is>
       </c>
       <c r="G39" s="7" t="n">
-        <v>31500</v>
+        <v>5250</v>
       </c>
       <c r="H39" s="7" t="n">
-        <v>31500</v>
+        <v>0</v>
       </c>
       <c r="I39" s="7" t="n">
-        <v>0</v>
+        <v>5250</v>
       </c>
     </row>
     <row r="40" ht="19" customHeight="1">
       <c r="A40" s="9" t="inlineStr">
         <is>
-          <t>2285</t>
+          <t>2336</t>
         </is>
       </c>
       <c r="B40" s="9" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="C40" s="9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D40" s="9" t="inlineStr">
         <is>
-          <t>3101010084</t>
+          <t>3201010028</t>
         </is>
       </c>
       <c r="E40" s="10" t="inlineStr">
         <is>
-          <t>Plastic XL Cap</t>
+          <t>Body Carton -Hero (3601)-195x195x230mm</t>
         </is>
       </c>
       <c r="F40" s="9" t="inlineStr">
@@ -2768,39 +2734,39 @@
         </is>
       </c>
       <c r="G40" s="11" t="n">
-        <v>42000</v>
+        <v>10500</v>
       </c>
       <c r="H40" s="11" t="n">
-        <v>12000</v>
+        <v>0</v>
       </c>
       <c r="I40" s="11" t="n">
-        <v>30000</v>
+        <v>10500</v>
       </c>
     </row>
     <row r="41" ht="19" customHeight="1">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>2285</t>
+          <t>2336</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>3101010085</t>
+          <t>3201010030</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>Insulation Rubber</t>
+          <t>Blade Carton-Premium (5601)-622x153x34mm</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
@@ -2809,39 +2775,39 @@
         </is>
       </c>
       <c r="G41" s="7" t="n">
-        <v>42000</v>
+        <v>24675</v>
       </c>
       <c r="H41" s="7" t="n">
-        <v>38582</v>
+        <v>0</v>
       </c>
       <c r="I41" s="7" t="n">
-        <v>3418</v>
+        <v>24675</v>
       </c>
     </row>
     <row r="42" ht="19" customHeight="1">
       <c r="A42" s="9" t="inlineStr">
         <is>
-          <t>2285</t>
+          <t>2336</t>
         </is>
       </c>
       <c r="B42" s="9" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="C42" s="9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D42" s="9" t="inlineStr">
         <is>
-          <t>3101010086</t>
+          <t>3201010031</t>
         </is>
       </c>
       <c r="E42" s="10" t="inlineStr">
         <is>
-          <t>Canopy Rubber Ring</t>
+          <t>Blade Carton-Premium Gold (5603)</t>
         </is>
       </c>
       <c r="F42" s="9" t="inlineStr">
@@ -2850,39 +2816,39 @@
         </is>
       </c>
       <c r="G42" s="11" t="n">
-        <v>84000</v>
+        <v>1050</v>
       </c>
       <c r="H42" s="11" t="n">
-        <v>72550</v>
+        <v>0</v>
       </c>
       <c r="I42" s="11" t="n">
-        <v>11450</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="43" ht="19" customHeight="1">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>2285</t>
+          <t>2336</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>3101010110</t>
+          <t>3201010034</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>Rubber Gasket (5602)</t>
+          <t>Blade Carton -Speed king (5602)-622x127x30mm</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
@@ -2891,39 +2857,39 @@
         </is>
       </c>
       <c r="G43" s="7" t="n">
-        <v>31500</v>
+        <v>5250</v>
       </c>
       <c r="H43" s="7" t="n">
-        <v>30406</v>
+        <v>0</v>
       </c>
       <c r="I43" s="7" t="n">
-        <v>1094</v>
+        <v>5250</v>
       </c>
     </row>
     <row r="44" ht="19" customHeight="1">
       <c r="A44" s="9" t="inlineStr">
         <is>
-          <t>2283</t>
+          <t>2336</t>
         </is>
       </c>
       <c r="B44" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="C44" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D44" s="9" t="inlineStr">
         <is>
-          <t>3201010002</t>
+          <t>3201010036</t>
         </is>
       </c>
       <c r="E44" s="10" t="inlineStr">
         <is>
-          <t>FAN Shank Paper</t>
+          <t>Blade Carton -Hero (3601)-400x120x29mm</t>
         </is>
       </c>
       <c r="F44" s="9" t="inlineStr">
@@ -2932,285 +2898,285 @@
         </is>
       </c>
       <c r="G44" s="11" t="n">
-        <v>129780</v>
+        <v>10500</v>
       </c>
       <c r="H44" s="11" t="n">
-        <v>110000</v>
+        <v>0</v>
       </c>
       <c r="I44" s="11" t="n">
-        <v>19780</v>
+        <v>10500</v>
       </c>
     </row>
     <row r="45" ht="19" customHeight="1">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>2283</t>
+          <t>2336</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>3201010006</t>
+          <t>3201010037</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>Body Sticker Speed King</t>
+          <t>HDPE Poly (L=15``, W=15``, T=0.035mm)</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>Pcs</t>
+          <t>KG</t>
         </is>
       </c>
       <c r="G45" s="7" t="n">
-        <v>10500</v>
+        <v>200</v>
       </c>
       <c r="H45" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I45" s="7" t="n">
-        <v>10500</v>
+        <v>200</v>
       </c>
     </row>
     <row r="46" ht="19" customHeight="1">
       <c r="A46" s="9" t="inlineStr">
         <is>
-          <t>2283</t>
+          <t>2336</t>
         </is>
       </c>
       <c r="B46" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="C46" s="9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D46" s="9" t="inlineStr">
         <is>
-          <t>3201010008</t>
+          <t>3201010038</t>
         </is>
       </c>
       <c r="E46" s="10" t="inlineStr">
         <is>
-          <t>Body Sticker-3601</t>
+          <t>HDPE Poly (L=14``, W=12``,T=0.035mm)</t>
         </is>
       </c>
       <c r="F46" s="9" t="inlineStr">
         <is>
-          <t>Pcs</t>
+          <t>KG</t>
         </is>
       </c>
       <c r="G46" s="11" t="n">
-        <v>5000</v>
+        <v>100</v>
       </c>
       <c r="H46" s="11" t="n">
-        <v>4840</v>
+        <v>0</v>
       </c>
       <c r="I46" s="11" t="n">
-        <v>160</v>
+        <v>100</v>
       </c>
     </row>
     <row r="47" ht="19" customHeight="1">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>2283</t>
+          <t>2336</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>3201010010</t>
+          <t>3201010039</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>Fan Canopy Sticker</t>
+          <t>HDPE Poly (L=27``, W=8``, T=0.035mm)</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>Pcs</t>
+          <t>KG</t>
         </is>
       </c>
       <c r="G47" s="7" t="n">
-        <v>60000</v>
+        <v>300</v>
       </c>
       <c r="H47" s="7" t="n">
-        <v>60000</v>
+        <v>0</v>
       </c>
       <c r="I47" s="7" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
     </row>
     <row r="48" ht="19" customHeight="1">
       <c r="A48" s="9" t="inlineStr">
         <is>
-          <t>2283</t>
+          <t>2336</t>
         </is>
       </c>
       <c r="B48" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="C48" s="9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D48" s="9" t="inlineStr">
         <is>
-          <t>3201010011</t>
+          <t>3201010041</t>
         </is>
       </c>
       <c r="E48" s="10" t="inlineStr">
         <is>
-          <t>Canopy Sticker Speed King</t>
+          <t>HDPE Poly (L=9``, W=9``, T=0.025mm)</t>
         </is>
       </c>
       <c r="F48" s="9" t="inlineStr">
         <is>
-          <t>Pcs</t>
+          <t>KG</t>
         </is>
       </c>
       <c r="G48" s="11" t="n">
-        <v>20000</v>
+        <v>125</v>
       </c>
       <c r="H48" s="11" t="n">
-        <v>7500</v>
+        <v>0</v>
       </c>
       <c r="I48" s="11" t="n">
-        <v>12500</v>
+        <v>125</v>
       </c>
     </row>
     <row r="49" ht="19" customHeight="1">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>2283</t>
+          <t>2336</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>3201010013</t>
+          <t>3201010042</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>Fan Down Pipe Sticker</t>
+          <t>HDPE Poly (L=13``, W=4``, T=0.035mm)</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>Pcs</t>
+          <t>KG</t>
         </is>
       </c>
       <c r="G49" s="7" t="n">
-        <v>21000</v>
+        <v>125</v>
       </c>
       <c r="H49" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I49" s="7" t="n">
-        <v>21000</v>
+        <v>125</v>
       </c>
     </row>
     <row r="50" ht="19" customHeight="1">
       <c r="A50" s="9" t="inlineStr">
         <is>
-          <t>2283</t>
+          <t>2336</t>
         </is>
       </c>
       <c r="B50" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="C50" s="9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D50" s="9" t="inlineStr">
         <is>
-          <t>3201010014</t>
+          <t>3201010043</t>
         </is>
       </c>
       <c r="E50" s="10" t="inlineStr">
         <is>
-          <t>Fan QC Sticker</t>
+          <t>PP Poly (L=5``, W=5``, T=0.045mm) With Logo Print</t>
         </is>
       </c>
       <c r="F50" s="9" t="inlineStr">
         <is>
-          <t>Pcs</t>
+          <t>KG</t>
         </is>
       </c>
       <c r="G50" s="11" t="n">
-        <v>43000</v>
+        <v>50</v>
       </c>
       <c r="H50" s="11" t="n">
-        <v>43000</v>
+        <v>0</v>
       </c>
       <c r="I50" s="11" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="51" ht="19" customHeight="1">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>2283</t>
+          <t>2336</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>3201010015</t>
+          <t>3201010051</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>Guarantee Card -5601</t>
+          <t>Body Sticker - 5603</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
@@ -3219,39 +3185,39 @@
         </is>
       </c>
       <c r="G51" s="7" t="n">
-        <v>21210</v>
+        <v>5000</v>
       </c>
       <c r="H51" s="7" t="n">
-        <v>21210</v>
+        <v>0</v>
       </c>
       <c r="I51" s="7" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="52" ht="19" customHeight="1">
       <c r="A52" s="9" t="inlineStr">
         <is>
-          <t>2283</t>
+          <t>2336</t>
         </is>
       </c>
       <c r="B52" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="C52" s="9" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>27</t>
         </is>
       </c>
       <c r="D52" s="9" t="inlineStr">
         <is>
-          <t>3201010017</t>
+          <t>3201010057</t>
         </is>
       </c>
       <c r="E52" s="10" t="inlineStr">
         <is>
-          <t>Guarantee Card Speed King</t>
+          <t>Body Carton - Crown (5607)</t>
         </is>
       </c>
       <c r="F52" s="9" t="inlineStr">
@@ -3260,39 +3226,39 @@
         </is>
       </c>
       <c r="G52" s="11" t="n">
-        <v>10500</v>
+        <v>200</v>
       </c>
       <c r="H52" s="11" t="n">
-        <v>10500</v>
+        <v>0</v>
       </c>
       <c r="I52" s="11" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
     </row>
     <row r="53" ht="19" customHeight="1">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>2283</t>
+          <t>2336</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>28</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>3201010018</t>
+          <t>3201010058</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>Guarantee Card -2401,3601</t>
+          <t>Blade Carton - Crown (5607)</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
@@ -3301,39 +3267,39 @@
         </is>
       </c>
       <c r="G53" s="7" t="n">
-        <v>10500</v>
+        <v>200</v>
       </c>
       <c r="H53" s="7" t="n">
-        <v>10500</v>
+        <v>0</v>
       </c>
       <c r="I53" s="7" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
     </row>
     <row r="54" ht="19" customHeight="1">
       <c r="A54" s="9" t="inlineStr">
         <is>
-          <t>2283</t>
+          <t>2336</t>
         </is>
       </c>
       <c r="B54" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="C54" s="9" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>29</t>
         </is>
       </c>
       <c r="D54" s="9" t="inlineStr">
         <is>
-          <t>3201010019</t>
+          <t>3201010059</t>
         </is>
       </c>
       <c r="E54" s="10" t="inlineStr">
         <is>
-          <t>Cork Sheet -5601````/4801````</t>
+          <t>Body Sticker (5607)</t>
         </is>
       </c>
       <c r="F54" s="9" t="inlineStr">
@@ -3342,39 +3308,39 @@
         </is>
       </c>
       <c r="G54" s="11" t="n">
-        <v>21210</v>
+        <v>2000</v>
       </c>
       <c r="H54" s="11" t="n">
-        <v>12600</v>
+        <v>0</v>
       </c>
       <c r="I54" s="11" t="n">
-        <v>8610</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="55" ht="19" customHeight="1">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>2283</t>
+          <t>2336</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>30</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>3201010020</t>
+          <t>3201010060</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
-          <t>Cork Sheet -5602````</t>
+          <t>Guarantee Card - Crown (5607)</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
@@ -3383,39 +3349,39 @@
         </is>
       </c>
       <c r="G55" s="7" t="n">
-        <v>10500</v>
+        <v>2000</v>
       </c>
       <c r="H55" s="7" t="n">
-        <v>8400</v>
+        <v>0</v>
       </c>
       <c r="I55" s="7" t="n">
-        <v>2100</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="56" ht="19" customHeight="1">
       <c r="A56" s="9" t="inlineStr">
         <is>
-          <t>2283</t>
+          <t>2336</t>
         </is>
       </c>
       <c r="B56" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="C56" s="9" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>31</t>
         </is>
       </c>
       <c r="D56" s="9" t="inlineStr">
         <is>
-          <t>3201010021</t>
+          <t>3201010064</t>
         </is>
       </c>
       <c r="E56" s="10" t="inlineStr">
         <is>
-          <t>Cork Sheet -2401/3601</t>
+          <t>Guarantee Card -5603</t>
         </is>
       </c>
       <c r="F56" s="9" t="inlineStr">
@@ -3424,39 +3390,39 @@
         </is>
       </c>
       <c r="G56" s="11" t="n">
-        <v>10500</v>
+        <v>5000</v>
       </c>
       <c r="H56" s="11" t="n">
-        <v>6550</v>
+        <v>0</v>
       </c>
       <c r="I56" s="11" t="n">
-        <v>3950</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="57" ht="19" customHeight="1">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>2283</t>
+          <t>2336</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>32</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>3201010022</t>
+          <t>3201010084</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
         <is>
-          <t>Body Carton -Premium (5601)-263x264x213mm</t>
+          <t>Guarantee Card -3601</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
@@ -3465,285 +3431,285 @@
         </is>
       </c>
       <c r="G57" s="7" t="n">
-        <v>18900</v>
+        <v>10500</v>
       </c>
       <c r="H57" s="7" t="n">
-        <v>2875</v>
+        <v>0</v>
       </c>
       <c r="I57" s="7" t="n">
-        <v>16025</v>
+        <v>10500</v>
       </c>
     </row>
     <row r="58" ht="19" customHeight="1">
       <c r="A58" s="9" t="inlineStr">
         <is>
-          <t>2283</t>
+          <t>2335</t>
         </is>
       </c>
       <c r="B58" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="C58" s="9" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D58" s="9" t="inlineStr">
         <is>
-          <t>3201010023</t>
+          <t>3101010016</t>
         </is>
       </c>
       <c r="E58" s="10" t="inlineStr">
         <is>
-          <t>Body Carton Premium Gold (5603)</t>
+          <t>Super Wire (SWG 33) / 0.253mm</t>
         </is>
       </c>
       <c r="F58" s="9" t="inlineStr">
         <is>
-          <t>Pcs</t>
+          <t>KG</t>
         </is>
       </c>
       <c r="G58" s="11" t="n">
-        <v>2500</v>
+        <v>9000</v>
       </c>
       <c r="H58" s="11" t="n">
-        <v>1650</v>
+        <v>0</v>
       </c>
       <c r="I58" s="11" t="n">
-        <v>850</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="59" ht="19" customHeight="1">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>2283</t>
+          <t>2335</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>3201010024</t>
+          <t>3101010017</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
         <is>
-          <t>Body Carton Premium Plus (5606)</t>
+          <t>Super Wire (SWG 34) / 0.233mm</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>Pcs</t>
+          <t>KG</t>
         </is>
       </c>
       <c r="G59" s="7" t="n">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="H59" s="7" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="I59" s="7" t="n">
-        <v>261</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="60" ht="19" customHeight="1">
       <c r="A60" s="9" t="inlineStr">
         <is>
-          <t>2283</t>
+          <t>2335</t>
         </is>
       </c>
       <c r="B60" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="C60" s="9" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D60" s="9" t="inlineStr">
         <is>
-          <t>3201010026</t>
+          <t>3101010018</t>
         </is>
       </c>
       <c r="E60" s="10" t="inlineStr">
         <is>
-          <t>Body Carton -Speed king (5602) -220x220x208mm</t>
+          <t>Super Wire (SWG 35) / 0.213mm</t>
         </is>
       </c>
       <c r="F60" s="9" t="inlineStr">
         <is>
-          <t>Pcs</t>
+          <t>KG</t>
         </is>
       </c>
       <c r="G60" s="11" t="n">
-        <v>10500</v>
+        <v>3000</v>
       </c>
       <c r="H60" s="11" t="n">
-        <v>5520</v>
+        <v>0</v>
       </c>
       <c r="I60" s="11" t="n">
-        <v>4980</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="61" ht="19" customHeight="1">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>2283</t>
+          <t>2335</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>3201010028</t>
+          <t>3101010090</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
         <is>
-          <t>Body Carton -Hero (3601)-195x195x230mm</t>
+          <t>Flaxible Cable 14x0.0076 - Red</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>Pcs</t>
+          <t>Mtr</t>
         </is>
       </c>
       <c r="G61" s="7" t="n">
-        <v>10500</v>
+        <v>38400</v>
       </c>
       <c r="H61" s="7" t="n">
-        <v>5100</v>
+        <v>0</v>
       </c>
       <c r="I61" s="7" t="n">
-        <v>5400</v>
+        <v>38400</v>
       </c>
     </row>
     <row r="62" ht="19" customHeight="1">
       <c r="A62" s="9" t="inlineStr">
         <is>
-          <t>2283</t>
+          <t>2335</t>
         </is>
       </c>
       <c r="B62" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="C62" s="9" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D62" s="9" t="inlineStr">
         <is>
-          <t>3201010030</t>
+          <t>3101010111</t>
         </is>
       </c>
       <c r="E62" s="10" t="inlineStr">
         <is>
-          <t>Blade Carton-Premium (5601)-622x153x34mm</t>
+          <t>Flaxible Cable 14x0.0076 - Yellow</t>
         </is>
       </c>
       <c r="F62" s="9" t="inlineStr">
         <is>
-          <t>Pcs</t>
+          <t>Mtr</t>
         </is>
       </c>
       <c r="G62" s="11" t="n">
-        <v>18900</v>
+        <v>12900</v>
       </c>
       <c r="H62" s="11" t="n">
-        <v>6430</v>
+        <v>0</v>
       </c>
       <c r="I62" s="11" t="n">
-        <v>12470</v>
+        <v>12900</v>
       </c>
     </row>
     <row r="63" ht="19" customHeight="1">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>2283</t>
+          <t>2335</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>3201010031</t>
+          <t>3101010112</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
         <is>
-          <t>Blade Carton-Premium Gold (5603)</t>
+          <t>Flaxible Cable 14x0.0076 - Black</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>Pcs</t>
+          <t>Mtr</t>
         </is>
       </c>
       <c r="G63" s="7" t="n">
-        <v>2100</v>
+        <v>38400</v>
       </c>
       <c r="H63" s="7" t="n">
-        <v>1830</v>
+        <v>0</v>
       </c>
       <c r="I63" s="7" t="n">
-        <v>270</v>
+        <v>38400</v>
       </c>
     </row>
     <row r="64" ht="19" customHeight="1">
       <c r="A64" s="9" t="inlineStr">
         <is>
-          <t>2283</t>
+          <t>2334</t>
         </is>
       </c>
       <c r="B64" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="C64" s="9" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D64" s="9" t="inlineStr">
         <is>
-          <t>3201010032</t>
+          <t>3101010071</t>
         </is>
       </c>
       <c r="E64" s="10" t="inlineStr">
         <is>
-          <t>Blade Carton-Premium Plus (5606)</t>
+          <t>Down Pipe Bolt 8mm x 1.5```` (50/kg)</t>
         </is>
       </c>
       <c r="F64" s="9" t="inlineStr">
@@ -3752,39 +3718,39 @@
         </is>
       </c>
       <c r="G64" s="11" t="n">
-        <v>210</v>
+        <v>93450</v>
       </c>
       <c r="H64" s="11" t="n">
         <v>0</v>
       </c>
       <c r="I64" s="11" t="n">
-        <v>210</v>
+        <v>93450</v>
       </c>
     </row>
     <row r="65" ht="19" customHeight="1">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>2283</t>
+          <t>2334</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>3201010034</t>
+          <t>3101010072</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
         <is>
-          <t>Blade Carton -Speed king (5602)-622x127x30mm</t>
+          <t>Down Pipe Bolt 8mm x 2```` (45/kg)</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
@@ -3793,39 +3759,39 @@
         </is>
       </c>
       <c r="G65" s="7" t="n">
-        <v>10500</v>
+        <v>16275</v>
       </c>
       <c r="H65" s="7" t="n">
-        <v>3950</v>
+        <v>0</v>
       </c>
       <c r="I65" s="7" t="n">
-        <v>6550</v>
+        <v>16275</v>
       </c>
     </row>
     <row r="66" ht="19" customHeight="1">
       <c r="A66" s="9" t="inlineStr">
         <is>
-          <t>2283</t>
+          <t>2334</t>
         </is>
       </c>
       <c r="B66" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="C66" s="9" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D66" s="9" t="inlineStr">
         <is>
-          <t>3201010036</t>
+          <t>3101010073</t>
         </is>
       </c>
       <c r="E66" s="10" t="inlineStr">
         <is>
-          <t>Blade Carton -Hero (3601)-400x120x29mm</t>
+          <t>Down Pipe Sira Pin(Fan)</t>
         </is>
       </c>
       <c r="F66" s="9" t="inlineStr">
@@ -3834,39 +3800,39 @@
         </is>
       </c>
       <c r="G66" s="11" t="n">
-        <v>10500</v>
+        <v>30000</v>
       </c>
       <c r="H66" s="11" t="n">
-        <v>8670</v>
+        <v>0</v>
       </c>
       <c r="I66" s="11" t="n">
-        <v>1830</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="67" ht="19" customHeight="1">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>2283</t>
+          <t>2334</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>3201010037</t>
+          <t>3101010074</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
         <is>
-          <t>HDPE Poly (L=15``, W=15``, T=0.035mm)</t>
+          <t>Shaft/XL /Safity lock Screw 3/16x3/8```` (400/kg)</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
@@ -3875,39 +3841,39 @@
         </is>
       </c>
       <c r="G67" s="7" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="H67" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I67" s="7" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
     </row>
     <row r="68" ht="19" customHeight="1">
       <c r="A68" s="9" t="inlineStr">
         <is>
-          <t>2283</t>
+          <t>2334</t>
         </is>
       </c>
       <c r="B68" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="C68" s="9" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D68" s="9" t="inlineStr">
         <is>
-          <t>3201010038</t>
+          <t>3101010075</t>
         </is>
       </c>
       <c r="E68" s="10" t="inlineStr">
         <is>
-          <t>HDPE Poly (L=14``, W=12``,T=0.035mm)</t>
+          <t>Body Screw  18x6mm,H=10mm (200/kg)</t>
         </is>
       </c>
       <c r="F68" s="9" t="inlineStr">
@@ -3916,39 +3882,39 @@
         </is>
       </c>
       <c r="G68" s="11" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H68" s="11" t="n">
         <v>0</v>
       </c>
       <c r="I68" s="11" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="69" ht="19" customHeight="1">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>2283</t>
+          <t>2334</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>3201010039</t>
+          <t>3101010076</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
         <is>
-          <t>HDPE Poly (L=27``, W=8``, T=0.035mm)</t>
+          <t>Body Screw  15x6mm,H=10mm (230/kg)</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
@@ -3957,39 +3923,39 @@
         </is>
       </c>
       <c r="G69" s="7" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H69" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I69" s="7" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="70" ht="19" customHeight="1">
       <c r="A70" s="9" t="inlineStr">
         <is>
-          <t>2283</t>
+          <t>2334</t>
         </is>
       </c>
       <c r="B70" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="C70" s="9" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D70" s="9" t="inlineStr">
         <is>
-          <t>3201010040</t>
+          <t>3101010077</t>
         </is>
       </c>
       <c r="E70" s="10" t="inlineStr">
         <is>
-          <t>HDPE Poly (L=18``, W=7``, T=0.035mm)</t>
+          <t>Blade/Body Screw 12.7x6mm,H=10mm (220/kg)</t>
         </is>
       </c>
       <c r="F70" s="9" t="inlineStr">
@@ -3998,39 +3964,39 @@
         </is>
       </c>
       <c r="G70" s="11" t="n">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="H70" s="11" t="n">
         <v>0</v>
       </c>
       <c r="I70" s="11" t="n">
-        <v>0</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="71" ht="19" customHeight="1">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>2283</t>
+          <t>2334</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>3201010041</t>
+          <t>3101010130</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
         <is>
-          <t>HDPE Poly (L=9``, W=9``, T=0.025mm)</t>
+          <t>Body screw- 3/16`` x 35mm</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
@@ -4039,39 +4005,39 @@
         </is>
       </c>
       <c r="G71" s="7" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H71" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I71" s="7" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="72" ht="19" customHeight="1">
       <c r="A72" s="9" t="inlineStr">
         <is>
-          <t>2283</t>
+          <t>2334</t>
         </is>
       </c>
       <c r="B72" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="C72" s="9" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D72" s="9" t="inlineStr">
         <is>
-          <t>3201010042</t>
+          <t>3102010013</t>
         </is>
       </c>
       <c r="E72" s="10" t="inlineStr">
         <is>
-          <t>HDPE Poly (L=13``, W=4``, T=0.035mm)</t>
+          <t>5/32 Inch, 9mm Screw</t>
         </is>
       </c>
       <c r="F72" s="9" t="inlineStr">
@@ -4080,80 +4046,80 @@
         </is>
       </c>
       <c r="G72" s="11" t="n">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="H72" s="11" t="n">
         <v>0</v>
       </c>
       <c r="I72" s="11" t="n">
-        <v>0</v>
+        <v>115</v>
       </c>
     </row>
     <row r="73" ht="19" customHeight="1">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>2283</t>
+          <t>2333</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>3201010043</t>
+          <t>3101010078</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
         <is>
-          <t>PP Poly (L=5``, W=5``, T=0.045mm) With Logo Print</t>
+          <t>Canopy Big</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>KG</t>
+          <t>Pcs</t>
         </is>
       </c>
       <c r="G73" s="7" t="n">
-        <v>0</v>
+        <v>82950</v>
       </c>
       <c r="H73" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I73" s="7" t="n">
-        <v>0</v>
+        <v>82950</v>
       </c>
     </row>
     <row r="74" ht="19" customHeight="1">
       <c r="A74" s="9" t="inlineStr">
         <is>
-          <t>2283</t>
+          <t>2333</t>
         </is>
       </c>
       <c r="B74" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="C74" s="9" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D74" s="9" t="inlineStr">
         <is>
-          <t>3201010051</t>
+          <t>3101010080</t>
         </is>
       </c>
       <c r="E74" s="10" t="inlineStr">
         <is>
-          <t>Body Sticker - 5603</t>
+          <t>Capacitor Cover</t>
         </is>
       </c>
       <c r="F74" s="9" t="inlineStr">
@@ -4162,39 +4128,39 @@
         </is>
       </c>
       <c r="G74" s="11" t="n">
-        <v>2500</v>
+        <v>40000</v>
       </c>
       <c r="H74" s="11" t="n">
-        <v>2500</v>
+        <v>0</v>
       </c>
       <c r="I74" s="11" t="n">
-        <v>0</v>
+        <v>40000</v>
       </c>
     </row>
     <row r="75" ht="19" customHeight="1">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>2283</t>
+          <t>2333</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>3201010057</t>
+          <t>3101010081</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
         <is>
-          <t>Body Carton - Crown (5607)</t>
+          <t>Rubber Gasket (56`` 48``)</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
@@ -4203,39 +4169,39 @@
         </is>
       </c>
       <c r="G75" s="7" t="n">
-        <v>1050</v>
+        <v>50000</v>
       </c>
       <c r="H75" s="7" t="n">
-        <v>1050</v>
+        <v>0</v>
       </c>
       <c r="I75" s="7" t="n">
-        <v>0</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="76" ht="19" customHeight="1">
       <c r="A76" s="9" t="inlineStr">
         <is>
-          <t>2283</t>
+          <t>2333</t>
         </is>
       </c>
       <c r="B76" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="C76" s="9" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D76" s="9" t="inlineStr">
         <is>
-          <t>3201010058</t>
+          <t>3101010084</t>
         </is>
       </c>
       <c r="E76" s="10" t="inlineStr">
         <is>
-          <t>Blade Carton - Crown (5607)</t>
+          <t>Plastic XL Cap</t>
         </is>
       </c>
       <c r="F76" s="9" t="inlineStr">
@@ -4244,39 +4210,39 @@
         </is>
       </c>
       <c r="G76" s="11" t="n">
-        <v>1050</v>
+        <v>41475</v>
       </c>
       <c r="H76" s="11" t="n">
-        <v>982</v>
+        <v>0</v>
       </c>
       <c r="I76" s="11" t="n">
-        <v>68</v>
+        <v>41475</v>
       </c>
     </row>
     <row r="77" ht="19" customHeight="1">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>2283</t>
+          <t>2333</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>3201010059</t>
+          <t>3101010085</t>
         </is>
       </c>
       <c r="E77" s="5" t="inlineStr">
         <is>
-          <t>Body Sticker (5607)</t>
+          <t>Insulation Rubber</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
@@ -4285,39 +4251,39 @@
         </is>
       </c>
       <c r="G77" s="7" t="n">
-        <v>2000</v>
+        <v>10000</v>
       </c>
       <c r="H77" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I77" s="7" t="n">
-        <v>2000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="78" ht="19" customHeight="1">
       <c r="A78" s="9" t="inlineStr">
         <is>
-          <t>2283</t>
+          <t>2333</t>
         </is>
       </c>
       <c r="B78" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="C78" s="9" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D78" s="9" t="inlineStr">
         <is>
-          <t>3201010060</t>
+          <t>3101010086</t>
         </is>
       </c>
       <c r="E78" s="10" t="inlineStr">
         <is>
-          <t>Guarantee Card - Crown (5607)</t>
+          <t>Canopy Rubber Ring</t>
         </is>
       </c>
       <c r="F78" s="9" t="inlineStr">
@@ -4326,121 +4292,121 @@
         </is>
       </c>
       <c r="G78" s="11" t="n">
-        <v>1050</v>
+        <v>82950</v>
       </c>
       <c r="H78" s="11" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="I78" s="11" t="n">
-        <v>50</v>
+        <v>82950</v>
       </c>
     </row>
     <row r="79" ht="19" customHeight="1">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>2282</t>
+          <t>2333</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>3202010001</t>
+          <t>3101010110</t>
         </is>
       </c>
       <c r="E79" s="5" t="inlineStr">
         <is>
-          <t>HDPE Poly (L=22``, W=18``, T=0.025mm)</t>
+          <t>Rubber Gasket (5602)</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>KG</t>
+          <t>Pcs</t>
         </is>
       </c>
       <c r="G79" s="7" t="n">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="H79" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I79" s="7" t="n">
-        <v>0</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="80" ht="19" customHeight="1">
       <c r="A80" s="9" t="inlineStr">
         <is>
-          <t>2282</t>
+          <t>2326</t>
         </is>
       </c>
       <c r="B80" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="C80" s="9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D80" s="9" t="inlineStr">
         <is>
-          <t>3202010008</t>
+          <t>3201010073</t>
         </is>
       </c>
       <c r="E80" s="10" t="inlineStr">
         <is>
-          <t>HDPE Poly (L=24``, W=20``, T=0.025mm)</t>
+          <t>Capacitor Master Carton-Fan</t>
         </is>
       </c>
       <c r="F80" s="9" t="inlineStr">
         <is>
-          <t>KG</t>
+          <t>Pcs</t>
         </is>
       </c>
       <c r="G80" s="11" t="n">
-        <v>150</v>
+        <v>6500</v>
       </c>
       <c r="H80" s="11" t="n">
-        <v>144.3</v>
+        <v>2693</v>
       </c>
       <c r="I80" s="11" t="n">
-        <v>5.7</v>
+        <v>3807</v>
       </c>
     </row>
     <row r="81" ht="19" customHeight="1">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>2282</t>
+          <t>2326</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>3201010014</t>
+          <t>3201010074</t>
         </is>
       </c>
       <c r="E81" s="5" t="inlineStr">
         <is>
-          <t>Fan QC Sticker</t>
+          <t>Capacitor Inner box 2.5 µF -Fan</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
@@ -4449,39 +4415,39 @@
         </is>
       </c>
       <c r="G81" s="7" t="n">
-        <v>0</v>
+        <v>13000</v>
       </c>
       <c r="H81" s="7" t="n">
-        <v>0</v>
+        <v>7327</v>
       </c>
       <c r="I81" s="7" t="n">
-        <v>0</v>
+        <v>5673</v>
       </c>
     </row>
     <row r="82" ht="19" customHeight="1">
       <c r="A82" s="9" t="inlineStr">
         <is>
-          <t>2282</t>
+          <t>2326</t>
         </is>
       </c>
       <c r="B82" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="C82" s="9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D82" s="9" t="inlineStr">
         <is>
-          <t>3201010073</t>
+          <t>3201010075</t>
         </is>
       </c>
       <c r="E82" s="10" t="inlineStr">
         <is>
-          <t>Capacitor Master Carton-Fan</t>
+          <t>Capacitor Inner box 3.5 µF -Fan</t>
         </is>
       </c>
       <c r="F82" s="9" t="inlineStr">
@@ -4490,39 +4456,39 @@
         </is>
       </c>
       <c r="G82" s="11" t="n">
-        <v>3300</v>
+        <v>13000</v>
       </c>
       <c r="H82" s="11" t="n">
-        <v>3300</v>
+        <v>8992</v>
       </c>
       <c r="I82" s="11" t="n">
-        <v>0</v>
+        <v>4008</v>
       </c>
     </row>
     <row r="83" ht="19" customHeight="1">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>2282</t>
+          <t>2326</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>3201010074</t>
+          <t>3201010076</t>
         </is>
       </c>
       <c r="E83" s="5" t="inlineStr">
         <is>
-          <t>Capacitor Inner box 2.5 µF -Fan</t>
+          <t>Capacitor Warranty Card 2.5 µF -Fan</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
@@ -4531,10 +4497,10 @@
         </is>
       </c>
       <c r="G83" s="7" t="n">
-        <v>6130</v>
+        <v>155000</v>
       </c>
       <c r="H83" s="7" t="n">
-        <v>6130</v>
+        <v>155000</v>
       </c>
       <c r="I83" s="7" t="n">
         <v>0</v>
@@ -4543,27 +4509,27 @@
     <row r="84" ht="19" customHeight="1">
       <c r="A84" s="9" t="inlineStr">
         <is>
-          <t>2282</t>
+          <t>2326</t>
         </is>
       </c>
       <c r="B84" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="C84" s="9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D84" s="9" t="inlineStr">
         <is>
-          <t>3201010075</t>
+          <t>3201010077</t>
         </is>
       </c>
       <c r="E84" s="10" t="inlineStr">
         <is>
-          <t>Capacitor Inner box 3.5 µF -Fan</t>
+          <t>Capacitor Warranty Card 3.5 µF -Fan</t>
         </is>
       </c>
       <c r="F84" s="9" t="inlineStr">
@@ -4572,10 +4538,10 @@
         </is>
       </c>
       <c r="G84" s="11" t="n">
-        <v>7010</v>
+        <v>155000</v>
       </c>
       <c r="H84" s="11" t="n">
-        <v>7010</v>
+        <v>155000</v>
       </c>
       <c r="I84" s="11" t="n">
         <v>0</v>
@@ -4584,27 +4550,27 @@
     <row r="85" ht="19" customHeight="1">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>2282</t>
+          <t>2326</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>3201010076</t>
+          <t>700100035</t>
         </is>
       </c>
       <c r="E85" s="5" t="inlineStr">
         <is>
-          <t>Capacitor Warranty Card 2.5 µF -Fan</t>
+          <t>QC Pass Sticker (Fan)- Blue Color</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
@@ -4613,259 +4579,13 @@
         </is>
       </c>
       <c r="G85" s="7" t="n">
-        <v>73500</v>
+        <v>50000</v>
       </c>
       <c r="H85" s="7" t="n">
-        <v>73500</v>
+        <v>30000</v>
       </c>
       <c r="I85" s="7" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" ht="19" customHeight="1">
-      <c r="A86" s="9" t="inlineStr">
-        <is>
-          <t>2282</t>
-        </is>
-      </c>
-      <c r="B86" s="9" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="C86" s="9" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="D86" s="9" t="inlineStr">
-        <is>
-          <t>3201010077</t>
-        </is>
-      </c>
-      <c r="E86" s="10" t="inlineStr">
-        <is>
-          <t>Capacitor Warranty Card 3.5 µF -Fan</t>
-        </is>
-      </c>
-      <c r="F86" s="9" t="inlineStr">
-        <is>
-          <t>Pcs</t>
-        </is>
-      </c>
-      <c r="G86" s="11" t="n">
-        <v>50000</v>
-      </c>
-      <c r="H86" s="11" t="n">
-        <v>50000</v>
-      </c>
-      <c r="I86" s="11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" ht="19" customHeight="1">
-      <c r="A87" s="4" t="inlineStr">
-        <is>
-          <t>2282</t>
-        </is>
-      </c>
-      <c r="B87" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="C87" s="4" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="D87" s="4" t="inlineStr">
-        <is>
-          <t>3201010079</t>
-        </is>
-      </c>
-      <c r="E87" s="5" t="inlineStr">
-        <is>
-          <t>8 Inch Exhaust Fan Body Carton (Alu)</t>
-        </is>
-      </c>
-      <c r="F87" s="4" t="inlineStr">
-        <is>
-          <t>Pcs</t>
-        </is>
-      </c>
-      <c r="G87" s="7" t="n">
-        <v>7350</v>
-      </c>
-      <c r="H87" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I87" s="7" t="n">
-        <v>7350</v>
-      </c>
-    </row>
-    <row r="88" ht="19" customHeight="1">
-      <c r="A88" s="9" t="inlineStr">
-        <is>
-          <t>2282</t>
-        </is>
-      </c>
-      <c r="B88" s="9" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="C88" s="9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="D88" s="9" t="inlineStr">
-        <is>
-          <t>3201010080</t>
-        </is>
-      </c>
-      <c r="E88" s="10" t="inlineStr">
-        <is>
-          <t>10 Inch Exhaust Fan Body Carton (Alu)</t>
-        </is>
-      </c>
-      <c r="F88" s="9" t="inlineStr">
-        <is>
-          <t>Pcs</t>
-        </is>
-      </c>
-      <c r="G88" s="11" t="n">
-        <v>8400</v>
-      </c>
-      <c r="H88" s="11" t="n">
-        <v>3125</v>
-      </c>
-      <c r="I88" s="11" t="n">
-        <v>5275</v>
-      </c>
-    </row>
-    <row r="89" ht="19" customHeight="1">
-      <c r="A89" s="4" t="inlineStr">
-        <is>
-          <t>2282</t>
-        </is>
-      </c>
-      <c r="B89" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="C89" s="4" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="D89" s="4" t="inlineStr">
-        <is>
-          <t>3201010081</t>
-        </is>
-      </c>
-      <c r="E89" s="5" t="inlineStr">
-        <is>
-          <t>Aero Flow Sticker</t>
-        </is>
-      </c>
-      <c r="F89" s="4" t="inlineStr">
-        <is>
-          <t>Pcs</t>
-        </is>
-      </c>
-      <c r="G89" s="7" t="n">
-        <v>8000</v>
-      </c>
-      <c r="H89" s="7" t="n">
-        <v>8000</v>
-      </c>
-      <c r="I89" s="7" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" ht="19" customHeight="1">
-      <c r="A90" s="9" t="inlineStr">
-        <is>
-          <t>2282</t>
-        </is>
-      </c>
-      <c r="B90" s="9" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="C90" s="9" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="D90" s="9" t="inlineStr">
-        <is>
-          <t>3201010083</t>
-        </is>
-      </c>
-      <c r="E90" s="10" t="inlineStr">
-        <is>
-          <t>Warranty Card (Aero Flow)</t>
-        </is>
-      </c>
-      <c r="F90" s="9" t="inlineStr">
-        <is>
-          <t>Pcs</t>
-        </is>
-      </c>
-      <c r="G90" s="11" t="n">
-        <v>16000</v>
-      </c>
-      <c r="H90" s="11" t="n">
-        <v>16000</v>
-      </c>
-      <c r="I90" s="11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91" ht="19" customHeight="1">
-      <c r="A91" s="4" t="inlineStr">
-        <is>
-          <t>2282</t>
-        </is>
-      </c>
-      <c r="B91" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="C91" s="4" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="D91" s="4" t="inlineStr">
-        <is>
-          <t>700100035</t>
-        </is>
-      </c>
-      <c r="E91" s="5" t="inlineStr">
-        <is>
-          <t>QC Pass Sticker (Fan)- Blue Color</t>
-        </is>
-      </c>
-      <c r="F91" s="4" t="inlineStr">
-        <is>
-          <t>Pcs</t>
-        </is>
-      </c>
-      <c r="G91" s="7" t="n">
-        <v>100000</v>
-      </c>
-      <c r="H91" s="7" t="n">
-        <v>100000</v>
-      </c>
-      <c r="I91" s="7" t="n">
-        <v>0</v>
+        <v>20000</v>
       </c>
     </row>
   </sheetData>
